--- a/files/TCperCountries.xlsx
+++ b/files/TCperCountries.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t xml:space="preserve">Country     </t>
   </si>
@@ -26,91 +26,91 @@
     <t xml:space="preserve">USA            </t>
   </si>
   <si>
-    <t xml:space="preserve">52606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.77</t>
+    <t xml:space="preserve">51828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.75</t>
   </si>
   <si>
     <t xml:space="preserve">UNITED KINGDOM </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.26</t>
+    <t xml:space="preserve"> 2389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.75</t>
   </si>
   <si>
     <t xml:space="preserve">CANADA         </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.02</t>
+    <t xml:space="preserve"> 2093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.10</t>
   </si>
   <si>
     <t xml:space="preserve">AUSTRALIA      </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.91</t>
+    <t xml:space="preserve"> 2031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERMANY        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.24</t>
   </si>
   <si>
     <t xml:space="preserve">CHINA          </t>
   </si>
   <si>
-    <t xml:space="preserve"> 1351</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GERMANY        </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.41</t>
+    <t xml:space="preserve"> 1295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.53</t>
   </si>
   <si>
     <t xml:space="preserve">ITALY          </t>
   </si>
   <si>
-    <t xml:space="preserve">  918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.93</t>
+    <t xml:space="preserve">  897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.35</t>
   </si>
   <si>
     <t xml:space="preserve">SPAIN          </t>
   </si>
   <si>
-    <t xml:space="preserve">  827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.34</t>
+    <t xml:space="preserve">  758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW ZEALAND    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.70</t>
   </si>
   <si>
     <t xml:space="preserve">NETHERLANDS    </t>
   </si>
   <si>
-    <t xml:space="preserve">  684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW ZEALAND    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.09</t>
+    <t xml:space="preserve">  677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.02</t>
   </si>
   <si>
     <t xml:space="preserve">TURKEY         </t>
@@ -128,43 +128,43 @@
     <t xml:space="preserve">  559</t>
   </si>
   <si>
-    <t xml:space="preserve">25.41</t>
+    <t xml:space="preserve">26.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRELAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWEDEN         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.38</t>
   </si>
   <si>
     <t xml:space="preserve">JAPAN          </t>
   </si>
   <si>
-    <t xml:space="preserve">  451</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRELAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWEDEN         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.63</t>
+    <t xml:space="preserve">  380</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7.31</t>
   </si>
   <si>
     <t xml:space="preserve">KOREA          </t>
   </si>
   <si>
-    <t xml:space="preserve">  248</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8.86</t>
+    <t xml:space="preserve">  245</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.07</t>
   </si>
   <si>
     <t xml:space="preserve">MEXICO         </t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">  228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.20</t>
+    <t xml:space="preserve">16.29</t>
   </si>
   <si>
     <t xml:space="preserve">GEORGIA        </t>
@@ -194,79 +194,82 @@
     <t xml:space="preserve">10.76</t>
   </si>
   <si>
+    <t xml:space="preserve">SINGAPORE      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUTH AFRICA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.62</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRAZIL         </t>
   </si>
   <si>
-    <t xml:space="preserve">  180</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOUTH AFRICA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SINGAPORE      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.56</t>
+    <t xml:space="preserve">  132</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREECE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDONESIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  111</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORWAY         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  110</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.50</t>
   </si>
   <si>
     <t xml:space="preserve">FRANCE         </t>
   </si>
   <si>
-    <t xml:space="preserve">  124</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORWAY         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREECE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDONESIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  111</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.17</t>
+    <t xml:space="preserve">  102</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   94</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.88</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYSIA       </t>
   </si>
   <si>
-    <t xml:space="preserve">10.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   96</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.05</t>
+    <t xml:space="preserve">10.44</t>
   </si>
   <si>
     <t xml:space="preserve">SAUDI ARABIA   </t>
@@ -278,22 +281,22 @@
     <t xml:space="preserve"> 5.56</t>
   </si>
   <si>
+    <t xml:space="preserve">FINLAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.25</t>
+  </si>
+  <si>
     <t xml:space="preserve">SWITZERLAND    </t>
   </si>
   <si>
-    <t xml:space="preserve">   67</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINLAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.80</t>
+    <t xml:space="preserve">   51</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8.50</t>
   </si>
   <si>
     <t xml:space="preserve">MALTA          </t>
@@ -308,25 +311,25 @@
     <t xml:space="preserve">ROMANIA        </t>
   </si>
   <si>
-    <t xml:space="preserve"> 9.60</t>
+    <t xml:space="preserve">12.00</t>
   </si>
   <si>
     <t xml:space="preserve">IRAN           </t>
   </si>
   <si>
-    <t xml:space="preserve">   40</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.82</t>
+    <t xml:space="preserve">   39</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.86</t>
   </si>
   <si>
     <t xml:space="preserve">COLOMBIA       </t>
   </si>
   <si>
-    <t xml:space="preserve">   39</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7.80</t>
+    <t xml:space="preserve">   38</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.50</t>
   </si>
   <si>
     <t xml:space="preserve">ICELAND        </t>
@@ -347,52 +350,43 @@
     <t xml:space="preserve"> 2.33</t>
   </si>
   <si>
-    <t xml:space="preserve">SLOVAKIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.00</t>
+    <t xml:space="preserve">CZECH REPUBLIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENMARK        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANZANIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAILAND       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.33</t>
   </si>
   <si>
     <t xml:space="preserve">AUSTRIA        </t>
   </si>
   <si>
-    <t xml:space="preserve">   20</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZECH REPUBLIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   15</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENMARK        </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TANZANIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THAILAND       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   13</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.33</t>
+    <t xml:space="preserve">   12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.40</t>
   </si>
   <si>
     <t xml:space="preserve">QATAR          </t>
@@ -401,39 +395,45 @@
     <t xml:space="preserve">   11</t>
   </si>
   <si>
-    <t xml:space="preserve"> 5.50</t>
+    <t xml:space="preserve">SRI LANKA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8.00</t>
   </si>
   <si>
     <t xml:space="preserve">PORTUGAL       </t>
   </si>
   <si>
-    <t xml:space="preserve">    8</t>
+    <t xml:space="preserve">    7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTONIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLAND         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U ARAB EMIRATES</t>
   </si>
   <si>
     <t xml:space="preserve"> 1.33</t>
   </si>
   <si>
-    <t xml:space="preserve">SRI LANKA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTONIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLAND         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U ARAB EMIRATES</t>
-  </si>
-  <si>
     <t xml:space="preserve">KUWAIT         </t>
   </si>
   <si>
@@ -459,18 +459,6 @@
   </si>
   <si>
     <t xml:space="preserve">SERBIA         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIETNAM        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUNGARY        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    1</t>
   </si>
   <si>
     <t xml:space="preserve">ECUADOR        </t>
@@ -1089,172 +1077,172 @@
         <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
         <v>82</v>
       </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
         <v>116</v>
@@ -1265,18 +1253,18 @@
         <v>117</v>
       </c>
       <c r="B41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" t="s">
         <v>118</v>
-      </c>
-      <c r="C41" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" t="s">
         <v>120</v>
-      </c>
-      <c r="B42" t="s">
-        <v>118</v>
       </c>
       <c r="C42" t="s">
         <v>121</v>
@@ -1287,21 +1275,21 @@
         <v>122</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45">
@@ -1331,175 +1319,142 @@
         <v>133</v>
       </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B48" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B51" t="s">
         <v>141</v>
       </c>
       <c r="C51" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B52" t="s">
         <v>141</v>
       </c>
       <c r="C52" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B53" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B54" t="s">
         <v>147</v>
       </c>
       <c r="C54" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>152</v>
+      </c>
+      <c r="B56" t="s">
         <v>150</v>
       </c>
-      <c r="B56" t="s">
-        <v>147</v>
-      </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
         <v>151</v>
-      </c>
-      <c r="B57" t="s">
-        <v>152</v>
-      </c>
-      <c r="C57" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C58" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>157</v>
-      </c>
-      <c r="B60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C60" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>158</v>
-      </c>
-      <c r="B61" t="s">
-        <v>154</v>
-      </c>
-      <c r="C61" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>159</v>
-      </c>
-      <c r="B62" t="s">
-        <v>154</v>
-      </c>
-      <c r="C62" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/files/TCperCountries.xlsx
+++ b/files/TCperCountries.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t xml:space="preserve">Country     </t>
   </si>
@@ -26,19 +26,19 @@
     <t xml:space="preserve">USA            </t>
   </si>
   <si>
-    <t xml:space="preserve">51828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.75</t>
+    <t xml:space="preserve">51499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.68</t>
   </si>
   <si>
     <t xml:space="preserve">UNITED KINGDOM </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.75</t>
+    <t xml:space="preserve"> 2379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.88</t>
   </si>
   <si>
     <t xml:space="preserve">CANADA         </t>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">AUSTRALIA      </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.13</t>
+    <t xml:space="preserve"> 2029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.45</t>
   </si>
   <si>
     <t xml:space="preserve">GERMANY        </t>
   </si>
   <si>
-    <t xml:space="preserve"> 1312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.24</t>
+    <t xml:space="preserve"> 1309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.48</t>
   </si>
   <si>
     <t xml:space="preserve">CHINA          </t>
   </si>
   <si>
-    <t xml:space="preserve"> 1295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.53</t>
+    <t xml:space="preserve"> 1235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.65</t>
   </si>
   <si>
     <t xml:space="preserve">ITALY          </t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">  758</t>
   </si>
   <si>
-    <t xml:space="preserve">12.03</t>
+    <t xml:space="preserve">12.23</t>
   </si>
   <si>
     <t xml:space="preserve">NEW ZEALAND    </t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">BELGIUM        </t>
   </si>
   <si>
-    <t xml:space="preserve">  559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.62</t>
+    <t xml:space="preserve">  558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.90</t>
   </si>
   <si>
     <t xml:space="preserve">IRELAND        </t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">KOREA          </t>
   </si>
   <si>
-    <t xml:space="preserve">  245</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9.07</t>
+    <t xml:space="preserve">  244</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.38</t>
   </si>
   <si>
     <t xml:space="preserve">MEXICO         </t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">SOUTH AFRICA   </t>
   </si>
   <si>
-    <t xml:space="preserve">  133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.62</t>
+    <t xml:space="preserve">  132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.86</t>
   </si>
   <si>
     <t xml:space="preserve">BRAZIL         </t>
   </si>
   <si>
-    <t xml:space="preserve">  132</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.71</t>
+    <t xml:space="preserve">  131</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.85</t>
   </si>
   <si>
     <t xml:space="preserve">GREECE         </t>
@@ -233,28 +233,25 @@
     <t xml:space="preserve">INDONESIA      </t>
   </si>
   <si>
-    <t xml:space="preserve">  111</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.17</t>
+    <t xml:space="preserve">  110</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.47</t>
   </si>
   <si>
     <t xml:space="preserve">NORWAY         </t>
   </si>
   <si>
-    <t xml:space="preserve">  110</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 5.50</t>
   </si>
   <si>
     <t xml:space="preserve">FRANCE         </t>
   </si>
   <si>
-    <t xml:space="preserve">  102</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.38</t>
+    <t xml:space="preserve">   98</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.53</t>
   </si>
   <si>
     <t xml:space="preserve">INDIA          </t>
@@ -269,7 +266,10 @@
     <t xml:space="preserve">MALAYSIA       </t>
   </si>
   <si>
-    <t xml:space="preserve">10.44</t>
+    <t xml:space="preserve">   93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.62</t>
   </si>
   <si>
     <t xml:space="preserve">SAUDI ARABIA   </t>
@@ -281,37 +281,37 @@
     <t xml:space="preserve"> 5.56</t>
   </si>
   <si>
+    <t xml:space="preserve">SWITZERLAND    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   51</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALTA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMANIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">FINLAND        </t>
   </si>
   <si>
-    <t xml:space="preserve">   53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWITZERLAND    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   51</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALTA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROMANIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.00</t>
+    <t xml:space="preserve">   41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.67</t>
   </si>
   <si>
     <t xml:space="preserve">IRAN           </t>
@@ -359,73 +359,70 @@
     <t xml:space="preserve"> 3.00</t>
   </si>
   <si>
+    <t xml:space="preserve">AUSTRIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAILAND       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QATAR          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   11</t>
+  </si>
+  <si>
     <t xml:space="preserve">DENMARK        </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2.14</t>
+    <t xml:space="preserve">    8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRI LANKA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTUGAL       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTONIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLAND         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.80</t>
   </si>
   <si>
     <t xml:space="preserve">TANZANIA       </t>
   </si>
   <si>
-    <t xml:space="preserve"> 7.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THAILAND       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   13</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUSTRIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   12</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QATAR          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRI LANKA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    8</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTUGAL       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    7</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTONIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    4</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLAND         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.80</t>
+    <t xml:space="preserve"> 4.00</t>
   </si>
   <si>
     <t xml:space="preserve">U ARAB EMIRATES</t>
@@ -1088,40 +1085,40 @@
         <v>75</v>
       </c>
       <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
         <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
         <v>78</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
         <v>81</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
         <v>84</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
       </c>
       <c r="C29" t="s">
         <v>85</v>
@@ -1165,18 +1162,18 @@
         <v>95</v>
       </c>
       <c r="B33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" t="s">
         <v>96</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
         <v>98</v>
-      </c>
-      <c r="B34" t="s">
-        <v>96</v>
       </c>
       <c r="C34" t="s">
         <v>99</v>
@@ -1242,32 +1239,32 @@
         <v>115</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
@@ -1286,10 +1283,10 @@
         <v>125</v>
       </c>
       <c r="B44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" t="s">
         <v>126</v>
-      </c>
-      <c r="C44" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="45">
@@ -1319,62 +1316,62 @@
         <v>133</v>
       </c>
       <c r="B47" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" t="s">
         <v>134</v>
-      </c>
-      <c r="C47" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" t="s">
         <v>136</v>
-      </c>
-      <c r="B48" t="s">
-        <v>134</v>
-      </c>
-      <c r="C48" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
         <v>138</v>
-      </c>
-      <c r="B49" t="s">
-        <v>134</v>
-      </c>
-      <c r="C49" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" t="s">
         <v>140</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>141</v>
-      </c>
-      <c r="C50" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" t="s">
         <v>143</v>
-      </c>
-      <c r="B51" t="s">
-        <v>141</v>
-      </c>
-      <c r="C51" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C52" t="s">
         <v>114</v>
@@ -1382,79 +1379,79 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" t="s">
         <v>146</v>
       </c>
-      <c r="B53" t="s">
-        <v>147</v>
-      </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C54" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>148</v>
+      </c>
+      <c r="B55" t="s">
         <v>149</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>150</v>
-      </c>
-      <c r="C55" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B56" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" t="s">
         <v>150</v>
-      </c>
-      <c r="C56" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B57" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" t="s">
         <v>150</v>
-      </c>
-      <c r="C57" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B58" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" t="s">
         <v>150</v>
-      </c>
-      <c r="C58" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B59" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" t="s">
         <v>150</v>
-      </c>
-      <c r="C59" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/files/TCperCountries.xlsx
+++ b/files/TCperCountries.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t xml:space="preserve">Country     </t>
   </si>
@@ -26,310 +26,310 @@
     <t xml:space="preserve">USA            </t>
   </si>
   <si>
-    <t xml:space="preserve">51499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.68</t>
+    <t xml:space="preserve">52605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.81</t>
   </si>
   <si>
     <t xml:space="preserve">UNITED KINGDOM </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.88</t>
+    <t xml:space="preserve"> 2370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.57</t>
   </si>
   <si>
     <t xml:space="preserve">CANADA         </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.10</t>
+    <t xml:space="preserve"> 2164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.65</t>
   </si>
   <si>
     <t xml:space="preserve">AUSTRALIA      </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.45</t>
+    <t xml:space="preserve"> 2067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHINA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.29</t>
   </si>
   <si>
     <t xml:space="preserve">GERMANY        </t>
   </si>
   <si>
-    <t xml:space="preserve"> 1309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHINA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.65</t>
+    <t xml:space="preserve"> 1338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.60</t>
   </si>
   <si>
     <t xml:space="preserve">ITALY          </t>
   </si>
   <si>
-    <t xml:space="preserve">  897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.35</t>
+    <t xml:space="preserve">  916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.04</t>
   </si>
   <si>
     <t xml:space="preserve">SPAIN          </t>
   </si>
   <si>
-    <t xml:space="preserve">  758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.23</t>
+    <t xml:space="preserve">  780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.58</t>
   </si>
   <si>
     <t xml:space="preserve">NEW ZEALAND    </t>
   </si>
   <si>
-    <t xml:space="preserve">  683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.70</t>
+    <t xml:space="preserve">  712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.58</t>
   </si>
   <si>
     <t xml:space="preserve">NETHERLANDS    </t>
   </si>
   <si>
-    <t xml:space="preserve">  677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.02</t>
+    <t xml:space="preserve">  711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.47</t>
   </si>
   <si>
     <t xml:space="preserve">TURKEY         </t>
   </si>
   <si>
-    <t xml:space="preserve">  665</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9.64</t>
+    <t xml:space="preserve">10.30</t>
   </si>
   <si>
     <t xml:space="preserve">BELGIUM        </t>
   </si>
   <si>
-    <t xml:space="preserve">  558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.90</t>
+    <t xml:space="preserve">  477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.85</t>
   </si>
   <si>
     <t xml:space="preserve">IRELAND        </t>
   </si>
   <si>
-    <t xml:space="preserve">  410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.83</t>
+    <t xml:space="preserve">  436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.17</t>
   </si>
   <si>
     <t xml:space="preserve">SWEDEN         </t>
   </si>
   <si>
-    <t xml:space="preserve">  387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.38</t>
+    <t xml:space="preserve">  415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.22</t>
   </si>
   <si>
     <t xml:space="preserve">JAPAN          </t>
   </si>
   <si>
-    <t xml:space="preserve">  380</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7.31</t>
+    <t xml:space="preserve">  396</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7.62</t>
   </si>
   <si>
     <t xml:space="preserve">KOREA          </t>
   </si>
   <si>
-    <t xml:space="preserve">  244</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9.38</t>
+    <t xml:space="preserve">  256</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.14</t>
   </si>
   <si>
     <t xml:space="preserve">MEXICO         </t>
   </si>
   <si>
-    <t xml:space="preserve">  235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.08</t>
+    <t xml:space="preserve">  250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.23</t>
   </si>
   <si>
     <t xml:space="preserve">ISRAEL         </t>
   </si>
   <si>
-    <t xml:space="preserve">  228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.29</t>
+    <t xml:space="preserve">  230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINGAPORE      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAZIL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  142</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUTH AFRICA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREECE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORWAY         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  122</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDONESIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  112</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  104</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAUDI ARABIA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  102</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  101</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALAYSIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   98</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.80</t>
   </si>
   <si>
     <t xml:space="preserve">GEORGIA        </t>
   </si>
   <si>
-    <t xml:space="preserve">  183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SINGAPORE      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOUTH AFRICA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRAZIL         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  131</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREECE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDONESIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  110</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORWAY         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRANCE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   98</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   94</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALAYSIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAUDI ARABIA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   89</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.56</t>
+    <t xml:space="preserve">   69</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.75</t>
   </si>
   <si>
     <t xml:space="preserve">SWITZERLAND    </t>
   </si>
   <si>
-    <t xml:space="preserve">   51</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8.50</t>
+    <t xml:space="preserve">   55</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAN           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   52</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.36</t>
   </si>
   <si>
     <t xml:space="preserve">MALTA          </t>
   </si>
   <si>
+    <t xml:space="preserve">52.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMANIA        </t>
+  </si>
+  <si>
     <t xml:space="preserve">   48</t>
   </si>
   <si>
-    <t xml:space="preserve">48.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROMANIA        </t>
-  </si>
-  <si>
     <t xml:space="preserve">16.00</t>
   </si>
   <si>
     <t xml:space="preserve">FINLAND        </t>
   </si>
   <si>
-    <t xml:space="preserve">   41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRAN           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   39</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.86</t>
+    <t xml:space="preserve">   47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.67</t>
   </si>
   <si>
     <t xml:space="preserve">COLOMBIA       </t>
   </si>
   <si>
-    <t xml:space="preserve">   38</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9.50</t>
+    <t xml:space="preserve">   42</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7.00</t>
   </si>
   <si>
     <t xml:space="preserve">ICELAND        </t>
@@ -344,120 +344,129 @@
     <t xml:space="preserve">CYPRUS         </t>
   </si>
   <si>
-    <t xml:space="preserve">   28</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.33</t>
+    <t xml:space="preserve">   30</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.50</t>
   </si>
   <si>
     <t xml:space="preserve">CZECH REPUBLIC </t>
   </si>
   <si>
-    <t xml:space="preserve">   15</t>
+    <t xml:space="preserve">   16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSTRIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QATAR          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAILAND       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENMARK        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRI LANKA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTUGAL       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANZANIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLAND         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U ARAB EMIRATES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTONIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KUWAIT         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LITHUANIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUNISIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERBIA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3</t>
   </si>
   <si>
     <t xml:space="preserve"> 3.00</t>
   </si>
   <si>
-    <t xml:space="preserve">AUSTRIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   12</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THAILAND       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QATAR          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENMARK        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    8</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRI LANKA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTUGAL       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    5</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTONIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    4</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLAND         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TANZANIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U ARAB EMIRATES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KUWAIT         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LITHUANIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUNISIA        </t>
-  </si>
-  <si>
     <t xml:space="preserve">PAKISTAN       </t>
   </si>
   <si>
     <t xml:space="preserve">    2</t>
   </si>
   <si>
-    <t xml:space="preserve">SERBIA         </t>
-  </si>
-  <si>
     <t xml:space="preserve">ECUADOR        </t>
   </si>
   <si>
@@ -468,6 +477,9 @@
   </si>
   <si>
     <t xml:space="preserve">EGYPT          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORDAN         </t>
   </si>
   <si>
     <t xml:space="preserve">KAZAKHSTAN     </t>
@@ -931,161 +943,161 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
         <v>48</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
         <v>51</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>52</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
         <v>54</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
         <v>57</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>64</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
         <v>66</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
         <v>69</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
         <v>72</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
         <v>75</v>
-      </c>
-      <c r="B26" t="s">
-        <v>73</v>
       </c>
       <c r="C26" t="s">
         <v>76</v>
@@ -1264,103 +1276,103 @@
         <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C46" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C48" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B49" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" t="s">
         <v>131</v>
-      </c>
-      <c r="C49" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B51" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s">
         <v>143</v>
@@ -1368,90 +1380,101 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C56" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>155</v>
+      </c>
+      <c r="B57" t="s">
         <v>152</v>
       </c>
-      <c r="B57" t="s">
-        <v>149</v>
-      </c>
       <c r="C57" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>156</v>
+      </c>
+      <c r="B58" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" t="s">
         <v>153</v>
-      </c>
-      <c r="B58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C58" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>150</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/files/TCperCountries.xlsx
+++ b/files/TCperCountries.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t xml:space="preserve">Country     </t>
   </si>
@@ -26,46 +26,46 @@
     <t xml:space="preserve">USA            </t>
   </si>
   <si>
-    <t xml:space="preserve">52605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.81</t>
+    <t xml:space="preserve">53842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.90</t>
   </si>
   <si>
     <t xml:space="preserve">UNITED KINGDOM </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.57</t>
+    <t xml:space="preserve"> 2532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.81</t>
   </si>
   <si>
     <t xml:space="preserve">CANADA         </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.65</t>
+    <t xml:space="preserve"> 2367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.66</t>
   </si>
   <si>
     <t xml:space="preserve">AUSTRALIA      </t>
   </si>
   <si>
-    <t xml:space="preserve"> 2067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.79</t>
+    <t xml:space="preserve"> 1886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.46</t>
   </si>
   <si>
     <t xml:space="preserve">CHINA          </t>
   </si>
   <si>
-    <t xml:space="preserve"> 1343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.29</t>
+    <t xml:space="preserve"> 1425</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.76</t>
   </si>
   <si>
     <t xml:space="preserve">GERMANY        </t>
@@ -74,25 +74,34 @@
     <t xml:space="preserve"> 1338</t>
   </si>
   <si>
-    <t xml:space="preserve">44.60</t>
+    <t xml:space="preserve">40.55</t>
   </si>
   <si>
     <t xml:space="preserve">ITALY          </t>
   </si>
   <si>
-    <t xml:space="preserve">  916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.04</t>
+    <t xml:space="preserve">  942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.21</t>
   </si>
   <si>
     <t xml:space="preserve">SPAIN          </t>
   </si>
   <si>
-    <t xml:space="preserve">  780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.58</t>
+    <t xml:space="preserve">  873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETHERLANDS    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.05</t>
   </si>
   <si>
     <t xml:space="preserve">NEW ZEALAND    </t>
@@ -104,28 +113,31 @@
     <t xml:space="preserve">21.58</t>
   </si>
   <si>
-    <t xml:space="preserve">NETHERLANDS    </t>
+    <t xml:space="preserve">TURKEY         </t>
   </si>
   <si>
     <t xml:space="preserve">  711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TURKEY         </t>
-  </si>
-  <si>
     <t xml:space="preserve">10.30</t>
   </si>
   <si>
     <t xml:space="preserve">BELGIUM        </t>
   </si>
   <si>
-    <t xml:space="preserve">  477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.85</t>
+    <t xml:space="preserve">  571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAPAN          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  454</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8.25</t>
   </si>
   <si>
     <t xml:space="preserve">IRELAND        </t>
@@ -140,28 +152,16 @@
     <t xml:space="preserve">SWEDEN         </t>
   </si>
   <si>
-    <t xml:space="preserve">  415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAPAN          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  396</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7.62</t>
+    <t xml:space="preserve">11.47</t>
   </si>
   <si>
     <t xml:space="preserve">KOREA          </t>
   </si>
   <si>
-    <t xml:space="preserve">  256</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9.14</t>
+    <t xml:space="preserve">  262</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8.73</t>
   </si>
   <si>
     <t xml:space="preserve">MEXICO         </t>
@@ -182,6 +182,15 @@
     <t xml:space="preserve">13.53</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAZIL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  160</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.71</t>
+  </si>
+  <si>
     <t xml:space="preserve">SINGAPORE      </t>
   </si>
   <si>
@@ -191,15 +200,6 @@
     <t xml:space="preserve">16.56</t>
   </si>
   <si>
-    <t xml:space="preserve">BRAZIL         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  142</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.73</t>
-  </si>
-  <si>
     <t xml:space="preserve">SOUTH AFRICA   </t>
   </si>
   <si>
@@ -209,40 +209,55 @@
     <t xml:space="preserve">15.56</t>
   </si>
   <si>
+    <t xml:space="preserve">NORWAY         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  133</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  127</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7.47</t>
+  </si>
+  <si>
     <t xml:space="preserve">GREECE         </t>
   </si>
   <si>
-    <t xml:space="preserve">  127</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.88</t>
   </si>
   <si>
-    <t xml:space="preserve">NORWAY         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  122</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5.55</t>
+    <t xml:space="preserve">MALAYSIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  115</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9.58</t>
   </si>
   <si>
     <t xml:space="preserve">INDONESIA      </t>
   </si>
   <si>
-    <t xml:space="preserve">  112</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.59</t>
+    <t xml:space="preserve">  113</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.28</t>
   </si>
   <si>
     <t xml:space="preserve">INDIA          </t>
   </si>
   <si>
-    <t xml:space="preserve">  104</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.12</t>
+    <t xml:space="preserve">  106</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.58</t>
   </si>
   <si>
     <t xml:space="preserve">SAUDI ARABIA   </t>
@@ -254,24 +269,6 @@
     <t xml:space="preserve"> 5.67</t>
   </si>
   <si>
-    <t xml:space="preserve">FRANCE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  101</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 7.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALAYSIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   98</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9.80</t>
-  </si>
-  <si>
     <t xml:space="preserve">GEORGIA        </t>
   </si>
   <si>
@@ -281,27 +278,39 @@
     <t xml:space="preserve"> 5.75</t>
   </si>
   <si>
+    <t xml:space="preserve">FINLAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.75</t>
+  </si>
+  <si>
     <t xml:space="preserve">SWITZERLAND    </t>
   </si>
   <si>
     <t xml:space="preserve">   55</t>
   </si>
   <si>
-    <t xml:space="preserve"> 6.11</t>
+    <t xml:space="preserve"> 5.50</t>
   </si>
   <si>
     <t xml:space="preserve">IRAN           </t>
   </si>
   <si>
+    <t xml:space="preserve">   54</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALTA          </t>
+  </si>
+  <si>
     <t xml:space="preserve">   52</t>
   </si>
   <si>
-    <t xml:space="preserve"> 2.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALTA          </t>
-  </si>
-  <si>
     <t xml:space="preserve">52.00</t>
   </si>
   <si>
@@ -311,16 +320,7 @@
     <t xml:space="preserve">   48</t>
   </si>
   <si>
-    <t xml:space="preserve">16.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINLAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.67</t>
+    <t xml:space="preserve"> 9.60</t>
   </si>
   <si>
     <t xml:space="preserve">COLOMBIA       </t>
@@ -350,6 +350,15 @@
     <t xml:space="preserve"> 2.50</t>
   </si>
   <si>
+    <t xml:space="preserve">SLOVAKIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">CZECH REPUBLIC </t>
   </si>
   <si>
@@ -359,6 +368,12 @@
     <t xml:space="preserve"> 3.20</t>
   </si>
   <si>
+    <t xml:space="preserve">DENMARK        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.29</t>
+  </si>
+  <si>
     <t xml:space="preserve">AUSTRIA        </t>
   </si>
   <si>
@@ -377,21 +392,6 @@
     <t xml:space="preserve">THAILAND       </t>
   </si>
   <si>
-    <t xml:space="preserve">   13</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENMARK        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   10</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.43</t>
-  </si>
-  <si>
     <t xml:space="preserve">SRI LANKA      </t>
   </si>
   <si>
@@ -407,37 +407,40 @@
     <t xml:space="preserve">    8</t>
   </si>
   <si>
+    <t xml:space="preserve"> 1.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANZANIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLAND         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U ARAB EMIRATES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTONIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 2.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TANZANIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    6</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLAND         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    5</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U ARAB EMIRATES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTONIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    4</t>
   </si>
   <si>
     <t xml:space="preserve">KUWAIT         </t>
@@ -943,51 +946,51 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1086,95 +1089,95 @@
         <v>71</v>
       </c>
       <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
         <v>72</v>
-      </c>
-      <c r="C25" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
         <v>74</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
         <v>77</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s">
         <v>80</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s">
         <v>83</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" t="s">
         <v>86</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>87</v>
-      </c>
-      <c r="C30" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
         <v>89</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>90</v>
-      </c>
-      <c r="C31" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
         <v>92</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
         <v>95</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
       </c>
       <c r="C33" t="s">
         <v>96</v>
@@ -1284,98 +1287,98 @@
         <v>123</v>
       </c>
       <c r="B43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" t="s">
         <v>124</v>
-      </c>
-      <c r="C43" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B48" t="s">
         <v>136</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C49" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B50" t="s">
         <v>141</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B51" t="s">
         <v>141</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52">
@@ -1386,7 +1389,7 @@
         <v>141</v>
       </c>
       <c r="C52" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53">
@@ -1394,43 +1397,43 @@
         <v>146</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" t="s">
         <v>149</v>
-      </c>
-      <c r="B54" t="s">
-        <v>150</v>
-      </c>
-      <c r="C54" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>150</v>
+      </c>
+      <c r="B55" t="s">
         <v>151</v>
       </c>
-      <c r="B55" t="s">
-        <v>152</v>
-      </c>
       <c r="C55" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>152</v>
+      </c>
+      <c r="B56" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" t="s">
         <v>154</v>
-      </c>
-      <c r="B56" t="s">
-        <v>152</v>
-      </c>
-      <c r="C56" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="57">
@@ -1438,10 +1441,10 @@
         <v>155</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58">
@@ -1449,10 +1452,10 @@
         <v>156</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59">
@@ -1460,10 +1463,10 @@
         <v>157</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60">
@@ -1471,10 +1474,21 @@
         <v>158</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>159</v>
+      </c>
+      <c r="B61" t="s">
         <v>153</v>
+      </c>
+      <c r="C61" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
